--- a/RAMON FRANCO/Octubre/CALCULO EDESUR RAMON FRANCO Octubre.xlsx
+++ b/RAMON FRANCO/Octubre/CALCULO EDESUR RAMON FRANCO Octubre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47608162-39A8-48C0-9FD8-602DAC9936AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B25AC0-F941-41D5-8373-376777E91A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -444,7 +444,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,6 +485,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -754,7 +766,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -890,7 +902,6 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -912,6 +923,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="8" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1232,11 +1263,11 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" customWidth="1"/>
     <col min="6" max="7" width="10.85546875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.42578125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="13" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="7.140625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="9.85546875" hidden="1" customWidth="1"/>
@@ -1250,22 +1281,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="100"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="113"/>
       <c r="O1" s="48"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3"/>
@@ -1418,18 +1449,18 @@
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="84">
-        <v>1328569.67</v>
+      <c r="C8" s="83">
+        <v>1062106.55</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="87">
+      <c r="J8" s="85"/>
+      <c r="K8" s="86">
         <f>C8-J32</f>
-        <v>805907.95712000038</v>
+        <v>613800.67879999964</v>
       </c>
       <c r="L8" s="47"/>
       <c r="M8" s="10"/>
@@ -1465,10 +1496,10 @@
       <c r="I9" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="90" t="s">
+      <c r="J9" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="90" t="s">
+      <c r="K9" s="89" t="s">
         <v>94</v>
       </c>
       <c r="L9" s="44" t="s">
@@ -1485,7 +1516,7 @@
       <c r="A10" s="59">
         <v>1</v>
       </c>
-      <c r="B10" s="95">
+      <c r="B10" s="94">
         <v>1</v>
       </c>
       <c r="C10" s="71" t="s">
@@ -1497,11 +1528,10 @@
       <c r="E10" s="73">
         <v>7.99</v>
       </c>
-      <c r="F10" s="96">
-        <f>+E10</f>
+      <c r="F10" s="95">
         <v>7.99</v>
       </c>
-      <c r="G10" s="96">
+      <c r="G10" s="95">
         <f>+F10</f>
         <v>7.99</v>
       </c>
@@ -1512,13 +1542,13 @@
         <f t="shared" ref="I10:I32" si="0">H10*7%</f>
         <v>0</v>
       </c>
-      <c r="J10" s="93">
+      <c r="J10" s="92">
         <f>M10*93.787</f>
         <v>0</v>
       </c>
-      <c r="K10" s="93">
+      <c r="K10" s="92">
         <f>K8*E10%</f>
-        <v>64392.045773888029</v>
+        <v>49042.674236119972</v>
       </c>
       <c r="L10" s="76"/>
       <c r="M10" s="77">
@@ -1527,54 +1557,54 @@
       </c>
       <c r="N10" s="78">
         <f>J10+K10+L10</f>
-        <v>64392.045773888029</v>
+        <v>49042.674236119972</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59">
         <v>2</v>
       </c>
-      <c r="B11" s="58">
+      <c r="B11" s="96">
         <v>2</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="99">
         <v>6.05</v>
       </c>
-      <c r="F11" s="94">
-        <v>490.1</v>
-      </c>
-      <c r="G11" s="94">
+      <c r="F11" s="100">
         <v>492.1</v>
       </c>
-      <c r="H11" s="54">
-        <v>0</v>
-      </c>
-      <c r="I11" s="55">
+      <c r="G11" s="100">
+        <v>494.5</v>
+      </c>
+      <c r="H11" s="101">
+        <v>0</v>
+      </c>
+      <c r="I11" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="91">
+      <c r="J11" s="103">
         <f>M11*173.944</f>
-        <v>347.88799999999998</v>
-      </c>
-      <c r="K11" s="91">
+        <v>417.46559999999602</v>
+      </c>
+      <c r="K11" s="103">
         <f>K8*E11%</f>
-        <v>48757.43140576002</v>
-      </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="57">
+        <v>37134.941067399981</v>
+      </c>
+      <c r="L11" s="104"/>
+      <c r="M11" s="105">
         <f t="shared" ref="M11:M31" si="1">G11-F11</f>
-        <v>2</v>
-      </c>
-      <c r="N11" s="69">
+        <v>2.3999999999999773</v>
+      </c>
+      <c r="N11" s="106">
         <f t="shared" ref="N11:N31" si="2">J11+K11+L11</f>
-        <v>49105.319405760019</v>
+        <v>37552.406667399977</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -1593,11 +1623,11 @@
       <c r="E12" s="53">
         <v>6.02</v>
       </c>
-      <c r="F12" s="94">
-        <v>4880.8999999999996</v>
-      </c>
-      <c r="G12" s="94">
+      <c r="F12" s="93">
         <v>5125.8999999999996</v>
+      </c>
+      <c r="G12" s="93">
+        <v>5161</v>
       </c>
       <c r="H12" s="54">
         <v>0</v>
@@ -1606,22 +1636,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="91">
+      <c r="J12" s="90">
         <f t="shared" ref="J12:J21" si="3">M12*173.944</f>
-        <v>42616.28</v>
-      </c>
-      <c r="K12" s="91">
+        <v>6105.4344000000629</v>
+      </c>
+      <c r="K12" s="90">
         <f>K8*E12%</f>
-        <v>48515.659018624021</v>
+        <v>36950.800863759978</v>
       </c>
       <c r="L12" s="56"/>
       <c r="M12" s="57">
         <f>G12-F12</f>
-        <v>245</v>
+        <v>35.100000000000364</v>
       </c>
       <c r="N12" s="69">
         <f t="shared" si="2"/>
-        <v>91131.93901862402</v>
+        <v>43056.235263760042</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -1640,28 +1670,27 @@
       <c r="E13" s="64">
         <v>7.63</v>
       </c>
-      <c r="F13" s="94">
-        <f>E13+250</f>
-        <v>257.63</v>
-      </c>
-      <c r="G13" s="94">
+      <c r="F13" s="93">
+        <v>507.63</v>
+      </c>
+      <c r="G13" s="93">
         <f>F13+250</f>
-        <v>507.63</v>
+        <v>757.63</v>
       </c>
       <c r="H13" s="65">
         <v>0</v>
       </c>
-      <c r="I13" s="85">
+      <c r="I13" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="91">
+      <c r="J13" s="90">
         <f t="shared" si="3"/>
         <v>43486</v>
       </c>
-      <c r="K13" s="92">
+      <c r="K13" s="91">
         <f>K8*E13%</f>
-        <v>61490.777128256021</v>
+        <v>46832.991792439971</v>
       </c>
       <c r="L13" s="56"/>
       <c r="M13" s="66">
@@ -1670,103 +1699,102 @@
       </c>
       <c r="N13" s="69">
         <f t="shared" si="2"/>
-        <v>104976.77712825601</v>
+        <v>90318.991792439978</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="59">
         <v>6</v>
       </c>
-      <c r="B14" s="58">
+      <c r="B14" s="96">
         <v>6</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="97" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="99">
         <v>6.05</v>
       </c>
-      <c r="F14" s="94">
-        <f>+E14+250</f>
-        <v>256.05</v>
-      </c>
-      <c r="G14" s="94">
+      <c r="F14" s="100">
+        <v>506.05</v>
+      </c>
+      <c r="G14" s="100">
         <f>+F14+250</f>
-        <v>506.05</v>
-      </c>
-      <c r="H14" s="54">
-        <v>0</v>
-      </c>
-      <c r="I14" s="55">
+        <v>756.05</v>
+      </c>
+      <c r="H14" s="101">
+        <v>0</v>
+      </c>
+      <c r="I14" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="91">
+      <c r="J14" s="103">
         <f t="shared" si="3"/>
-        <v>43486</v>
-      </c>
-      <c r="K14" s="91">
+        <v>43485.999999999985</v>
+      </c>
+      <c r="K14" s="103">
         <f>K8*E14%</f>
-        <v>48757.43140576002</v>
-      </c>
-      <c r="L14" s="56"/>
-      <c r="M14" s="57">
+        <v>37134.941067399981</v>
+      </c>
+      <c r="L14" s="104"/>
+      <c r="M14" s="105">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N14" s="69">
+        <v>249.99999999999994</v>
+      </c>
+      <c r="N14" s="106">
         <f>J14+K14+L14</f>
-        <v>92243.431405760028</v>
+        <v>80620.941067399966</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="59">
         <v>7</v>
       </c>
-      <c r="B15" s="58">
+      <c r="B15" s="96">
         <v>7</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="99">
         <v>6.02</v>
       </c>
-      <c r="F15" s="94">
-        <v>5019.8</v>
-      </c>
-      <c r="G15" s="94">
+      <c r="F15" s="100">
         <v>5182.8999999999996</v>
       </c>
-      <c r="H15" s="54">
-        <v>0</v>
-      </c>
-      <c r="I15" s="55">
+      <c r="G15" s="100">
+        <v>5383.3</v>
+      </c>
+      <c r="H15" s="101">
+        <v>0</v>
+      </c>
+      <c r="I15" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="91">
+      <c r="J15" s="103">
         <f t="shared" si="3"/>
-        <v>28370.266399999902</v>
-      </c>
-      <c r="K15" s="91">
+        <v>34858.377600000094</v>
+      </c>
+      <c r="K15" s="103">
         <f>K8*E15%</f>
-        <v>48515.659018624021</v>
-      </c>
-      <c r="L15" s="56"/>
-      <c r="M15" s="57">
+        <v>36950.800863759978</v>
+      </c>
+      <c r="L15" s="104"/>
+      <c r="M15" s="105">
         <f t="shared" si="1"/>
-        <v>163.09999999999945</v>
-      </c>
-      <c r="N15" s="69">
+        <v>200.40000000000055</v>
+      </c>
+      <c r="N15" s="106">
         <f t="shared" si="2"/>
-        <v>76885.925418623927</v>
+        <v>71809.178463760065</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -1785,11 +1813,11 @@
       <c r="E16" s="53">
         <v>7.63</v>
       </c>
-      <c r="F16" s="94">
-        <v>14922.1</v>
-      </c>
-      <c r="G16" s="94">
+      <c r="F16" s="93">
         <v>15267.9</v>
+      </c>
+      <c r="G16" s="93">
+        <v>15698.4</v>
       </c>
       <c r="H16" s="26">
         <v>0</v>
@@ -1798,22 +1826,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="91">
+      <c r="J16" s="90">
         <f t="shared" si="3"/>
-        <v>60149.83519999987</v>
-      </c>
-      <c r="K16" s="91">
+        <v>74882.891999999993</v>
+      </c>
+      <c r="K16" s="90">
         <f>K8*E16%</f>
-        <v>61490.777128256021</v>
+        <v>46832.991792439971</v>
       </c>
       <c r="L16" s="56"/>
       <c r="M16" s="57">
         <f t="shared" si="1"/>
-        <v>345.79999999999927</v>
+        <v>430.5</v>
       </c>
       <c r="N16" s="69">
         <f t="shared" si="2"/>
-        <v>121640.6123282559</v>
+        <v>121715.88379243997</v>
       </c>
       <c r="P16" s="50"/>
     </row>
@@ -1821,47 +1849,47 @@
       <c r="A17" s="59">
         <v>9</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="96">
         <v>9</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="97" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="52" t="s">
+      <c r="D17" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="99">
         <v>6.05</v>
       </c>
-      <c r="F17" s="94">
-        <v>10499.21</v>
-      </c>
-      <c r="G17" s="94">
+      <c r="F17" s="100">
         <v>10827.14</v>
       </c>
-      <c r="H17" s="54">
-        <v>0</v>
-      </c>
-      <c r="I17" s="55">
+      <c r="G17" s="100">
+        <v>10949.59</v>
+      </c>
+      <c r="H17" s="101">
+        <v>0</v>
+      </c>
+      <c r="I17" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="91">
+      <c r="J17" s="103">
         <f t="shared" si="3"/>
-        <v>57041.455920000044</v>
-      </c>
-      <c r="K17" s="91">
+        <v>21299.442800000124</v>
+      </c>
+      <c r="K17" s="103">
         <f>K8*E17%</f>
-        <v>48757.43140576002</v>
-      </c>
-      <c r="L17" s="56"/>
-      <c r="M17" s="57">
+        <v>37134.941067399981</v>
+      </c>
+      <c r="L17" s="104"/>
+      <c r="M17" s="105">
         <f t="shared" si="1"/>
-        <v>327.93000000000029</v>
-      </c>
-      <c r="N17" s="69">
+        <v>122.45000000000073</v>
+      </c>
+      <c r="N17" s="106">
         <f t="shared" si="2"/>
-        <v>105798.88732576006</v>
+        <v>58434.383867400102</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1880,12 +1908,12 @@
       <c r="E18" s="53">
         <v>6.02</v>
       </c>
-      <c r="F18" s="94">
-        <v>8492.7999999999993</v>
-      </c>
-      <c r="G18" s="94">
+      <c r="F18" s="93">
+        <v>8642.7999999999993</v>
+      </c>
+      <c r="G18" s="93">
         <f>F18+150</f>
-        <v>8642.7999999999993</v>
+        <v>8792.7999999999993</v>
       </c>
       <c r="H18" s="54">
         <v>0</v>
@@ -1894,13 +1922,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="91">
+      <c r="J18" s="90">
         <f t="shared" si="3"/>
         <v>26091.599999999999</v>
       </c>
-      <c r="K18" s="91">
+      <c r="K18" s="90">
         <f>K8*E18%</f>
-        <v>48515.659018624021</v>
+        <v>36950.800863759978</v>
       </c>
       <c r="L18" s="56"/>
       <c r="M18" s="57">
@@ -1909,7 +1937,7 @@
       </c>
       <c r="N18" s="69">
         <f t="shared" si="2"/>
-        <v>74607.259018624027</v>
+        <v>63042.400863759976</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1928,11 +1956,11 @@
       <c r="E19" s="67">
         <v>21.2</v>
       </c>
-      <c r="F19" s="94">
-        <v>23124.77</v>
-      </c>
-      <c r="G19" s="94">
+      <c r="F19" s="93">
         <v>23463.64</v>
+      </c>
+      <c r="G19" s="93">
+        <v>23696.95</v>
       </c>
       <c r="H19" s="26">
         <v>0</v>
@@ -1941,71 +1969,70 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="91">
+      <c r="J19" s="90">
         <f t="shared" si="3"/>
-        <v>58944.403279999817</v>
-      </c>
-      <c r="K19" s="91">
+        <v>40582.874640000227</v>
+      </c>
+      <c r="K19" s="90">
         <f>K8*E19%</f>
-        <v>170852.48690944008</v>
+        <v>130125.74390559993</v>
       </c>
       <c r="L19" s="56"/>
       <c r="M19" s="57">
         <f>G19-F19</f>
-        <v>338.86999999999898</v>
+        <v>233.31000000000131</v>
       </c>
       <c r="N19" s="69">
         <f t="shared" si="2"/>
-        <v>229796.8901894399</v>
+        <v>170708.61854560015</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="59">
         <v>12</v>
       </c>
-      <c r="B20" s="58">
+      <c r="B20" s="96">
         <v>12</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="60" t="s">
+      <c r="D20" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="99">
         <v>6.81</v>
       </c>
-      <c r="F20" s="94">
-        <f>E20+600</f>
-        <v>606.80999999999995</v>
-      </c>
-      <c r="G20" s="94">
+      <c r="F20" s="100">
+        <v>1206.81</v>
+      </c>
+      <c r="G20" s="100">
         <f>F20+600</f>
-        <v>1206.81</v>
-      </c>
-      <c r="H20" s="26">
-        <v>0</v>
-      </c>
-      <c r="I20" s="55">
+        <v>1806.81</v>
+      </c>
+      <c r="H20" s="109">
+        <v>0</v>
+      </c>
+      <c r="I20" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="91">
+      <c r="J20" s="103">
         <f t="shared" si="3"/>
         <v>104366.39999999999</v>
       </c>
-      <c r="K20" s="91">
+      <c r="K20" s="103">
         <f>K8*E20%</f>
-        <v>54882.331879872021</v>
-      </c>
-      <c r="L20" s="56"/>
-      <c r="M20" s="57">
+        <v>41799.826226279969</v>
+      </c>
+      <c r="L20" s="104"/>
+      <c r="M20" s="105">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="N20" s="69">
+      <c r="N20" s="106">
         <f t="shared" si="2"/>
-        <v>159248.73187987201</v>
+        <v>146166.22622627998</v>
       </c>
       <c r="P20" s="33"/>
     </row>
@@ -2025,11 +2052,11 @@
       <c r="E21" s="53">
         <v>6.52</v>
       </c>
-      <c r="F21" s="94">
-        <v>14907.93</v>
-      </c>
-      <c r="G21" s="94">
+      <c r="F21" s="93">
         <v>15240</v>
+      </c>
+      <c r="G21" s="93">
+        <v>15543.14</v>
       </c>
       <c r="H21" s="26">
         <v>0</v>
@@ -2038,22 +2065,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="91">
+      <c r="J21" s="90">
         <f t="shared" si="3"/>
-        <v>57761.584079999942</v>
-      </c>
-      <c r="K21" s="91">
+        <v>52729.384159999892</v>
+      </c>
+      <c r="K21" s="90">
         <f>K8*E21%</f>
-        <v>52545.198804224019</v>
+        <v>40019.80425775997</v>
       </c>
       <c r="L21" s="56"/>
       <c r="M21" s="57">
         <f t="shared" si="1"/>
-        <v>332.06999999999971</v>
+        <v>303.13999999999942</v>
       </c>
       <c r="N21" s="69">
         <f t="shared" si="2"/>
-        <v>110306.78288422397</v>
+        <v>92749.188417759869</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2085,13 +2112,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="93">
-        <f t="shared" ref="J11:J27" si="4">M22*93.787</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="93">
+      <c r="J22" s="92">
+        <f t="shared" ref="J22:J27" si="4">M22*93.787</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="92">
         <f>K8*E22%</f>
-        <v>9509.7138940160039</v>
+        <v>7242.8480098399959</v>
       </c>
       <c r="L22" s="76"/>
       <c r="M22" s="77">
@@ -2100,7 +2127,7 @@
       </c>
       <c r="N22" s="78">
         <f t="shared" si="2"/>
-        <v>9509.7138940160039</v>
+        <v>7242.8480098399959</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2132,13 +2159,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="93">
+      <c r="J23" s="92">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K23" s="93">
+      <c r="K23" s="92">
         <f>K8*E23%</f>
-        <v>9429.1230983040041</v>
+        <v>7181.4679419599952</v>
       </c>
       <c r="L23" s="76"/>
       <c r="M23" s="77">
@@ -2147,54 +2174,54 @@
       </c>
       <c r="N23" s="78">
         <f t="shared" si="2"/>
-        <v>9429.1230983040041</v>
+        <v>7181.4679419599952</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
         <v>16</v>
       </c>
-      <c r="B24" s="58">
+      <c r="B24" s="79">
         <v>16</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="53">
+      <c r="E24" s="73">
         <v>1.06</v>
       </c>
-      <c r="F24" s="59">
-        <v>0</v>
-      </c>
-      <c r="G24" s="59">
-        <v>0</v>
-      </c>
-      <c r="H24" s="54">
-        <v>0</v>
-      </c>
-      <c r="I24" s="55">
+      <c r="F24" s="80">
+        <v>0</v>
+      </c>
+      <c r="G24" s="80">
+        <v>0</v>
+      </c>
+      <c r="H24" s="74">
+        <v>0</v>
+      </c>
+      <c r="I24" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="91">
+      <c r="J24" s="92">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K24" s="91">
+      <c r="K24" s="92">
         <f>K8*E24%</f>
-        <v>8542.6243454720043</v>
-      </c>
-      <c r="L24" s="56"/>
-      <c r="M24" s="57">
+        <v>6506.287195279996</v>
+      </c>
+      <c r="L24" s="76"/>
+      <c r="M24" s="77">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N24" s="69">
+      <c r="N24" s="78">
         <f t="shared" si="2"/>
-        <v>8542.6243454720043</v>
+        <v>6506.287195279996</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2226,13 +2253,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="93">
+      <c r="J25" s="92">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K25" s="93">
+      <c r="K25" s="92">
         <f>K8*E25%</f>
-        <v>4110.1305813120025</v>
+        <v>3130.3834618799983</v>
       </c>
       <c r="L25" s="76"/>
       <c r="M25" s="82">
@@ -2241,7 +2268,7 @@
       </c>
       <c r="N25" s="78">
         <f t="shared" si="2"/>
-        <v>4110.1305813120025</v>
+        <v>3130.3834618799983</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2273,13 +2300,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="88">
+      <c r="J26" s="87">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K26" s="89">
+      <c r="K26" s="88">
         <f>K8*E26%</f>
-        <v>2175.951484224001</v>
+        <v>1657.2618327599992</v>
       </c>
       <c r="L26" s="45"/>
       <c r="M26" s="43">
@@ -2288,7 +2315,7 @@
       </c>
       <c r="N26" s="70">
         <f t="shared" si="2"/>
-        <v>2175.951484224001</v>
+        <v>1657.2618327599992</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2326,7 +2353,7 @@
       </c>
       <c r="K27" s="45">
         <f>K8*E27%</f>
-        <v>14667.524819584009</v>
+        <v>11171.172354159995</v>
       </c>
       <c r="L27" s="45"/>
       <c r="M27" s="43">
@@ -2335,7 +2362,7 @@
       </c>
       <c r="N27" s="70">
         <f t="shared" si="2"/>
-        <v>14667.524819584009</v>
+        <v>11171.172354159995</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2496,7 +2523,7 @@
       </c>
       <c r="G32" s="18">
         <f>SUM(G14:G31)+G13+G12+G11+G10</f>
-        <v>86470.86</v>
+        <v>89048.16</v>
       </c>
       <c r="H32" s="19">
         <v>0</v>
@@ -2507,11 +2534,11 @@
       </c>
       <c r="J32" s="41">
         <f>J27+J26+J25+J24+J23+J22+J21+J20+J19+J18+J17+J16+J15+J14+J13+J12+J11+J10</f>
-        <v>522661.7128799996</v>
+        <v>448305.87120000046</v>
       </c>
       <c r="K32" s="45">
         <f>K27+K26+K25+K24+K23+K22+K21+K20+K18+K19+K17+K16+K15+K14+K13+K12+K11+K10</f>
-        <v>805907.95712000027</v>
+        <v>613800.67879999964</v>
       </c>
       <c r="L32" s="45">
         <f>SUM(L10:L31)</f>
@@ -2519,11 +2546,11 @@
       </c>
       <c r="M32" s="43">
         <f>SUM(M14:M31)+M12+M13+M11+M10</f>
-        <v>3004.7699999999977</v>
+        <v>2577.3000000000025</v>
       </c>
       <c r="N32" s="19">
         <f>N27+N26+N25+N24+N23+N22+N21+N20+N19+N18+N17+N16+N15+N14+N13++N12+N11+N10</f>
-        <v>1328569.6699999997</v>
+        <v>1062106.55</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2543,7 +2570,7 @@
       </c>
       <c r="J33" s="30">
         <f>SUM(J10:J32)</f>
-        <v>1045323.4257599991</v>
+        <v>896611.7424000008</v>
       </c>
       <c r="K33" s="46"/>
       <c r="L33" s="46"/>
@@ -2553,7 +2580,7 @@
       </c>
       <c r="N33" s="29">
         <f>SUM(N10:N32)</f>
-        <v>2657139.34</v>
+        <v>2124213.1</v>
       </c>
       <c r="O33" s="5"/>
       <c r="P33" s="2" t="e">
@@ -2565,20 +2592,20 @@
       <c r="A34" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="101" t="s">
+      <c r="C34" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="99"/>
-      <c r="M34" s="98"/>
-      <c r="N34" s="99"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="111"/>
+      <c r="I34" s="111"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="112"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="111"/>
+      <c r="N34" s="112"/>
       <c r="O34" s="31"/>
       <c r="P34" s="2" t="e">
         <f t="shared" si="5"/>
@@ -2594,61 +2621,61 @@
       <c r="P35" s="2"/>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="102" t="s">
+      <c r="C36" s="115" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="102"/>
-      <c r="E36" s="102"/>
-      <c r="F36" s="102"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="102"/>
-      <c r="I36" s="102"/>
-      <c r="J36" s="102"/>
-      <c r="K36" s="102"/>
-      <c r="L36" s="102"/>
-      <c r="M36" s="102"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="115"/>
+      <c r="G36" s="115"/>
+      <c r="H36" s="115"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="115"/>
+      <c r="K36" s="115"/>
+      <c r="L36" s="115"/>
+      <c r="M36" s="115"/>
       <c r="P36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="102"/>
-      <c r="D37" s="102"/>
-      <c r="E37" s="102"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="102"/>
-      <c r="H37" s="102"/>
-      <c r="I37" s="102"/>
-      <c r="J37" s="102"/>
-      <c r="K37" s="102"/>
-      <c r="L37" s="102"/>
-      <c r="M37" s="102"/>
+      <c r="C37" s="115"/>
+      <c r="D37" s="115"/>
+      <c r="E37" s="115"/>
+      <c r="F37" s="115"/>
+      <c r="G37" s="115"/>
+      <c r="H37" s="115"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="115"/>
+      <c r="K37" s="115"/>
+      <c r="L37" s="115"/>
+      <c r="M37" s="115"/>
       <c r="P37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="102"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="102"/>
-      <c r="H38" s="102"/>
-      <c r="I38" s="102"/>
-      <c r="J38" s="102"/>
-      <c r="K38" s="102"/>
-      <c r="L38" s="102"/>
-      <c r="M38" s="102"/>
+      <c r="C38" s="115"/>
+      <c r="D38" s="115"/>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="115"/>
+      <c r="H38" s="115"/>
+      <c r="I38" s="115"/>
+      <c r="J38" s="115"/>
+      <c r="K38" s="115"/>
+      <c r="L38" s="115"/>
+      <c r="M38" s="115"/>
       <c r="P38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="102"/>
-      <c r="D39" s="102"/>
-      <c r="E39" s="102"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="102"/>
-      <c r="H39" s="102"/>
-      <c r="I39" s="102"/>
-      <c r="J39" s="102"/>
-      <c r="K39" s="102"/>
-      <c r="L39" s="102"/>
-      <c r="M39" s="102"/>
+      <c r="C39" s="115"/>
+      <c r="D39" s="115"/>
+      <c r="E39" s="115"/>
+      <c r="F39" s="115"/>
+      <c r="G39" s="115"/>
+      <c r="H39" s="115"/>
+      <c r="I39" s="115"/>
+      <c r="J39" s="115"/>
+      <c r="K39" s="115"/>
+      <c r="L39" s="115"/>
+      <c r="M39" s="115"/>
       <c r="P39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6528,21 +6555,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="110" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="100"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="113"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8134,19 +8161,19 @@
       <c r="A35" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="101" t="s">
+      <c r="C35" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="98"/>
-      <c r="H35" s="98"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="98"/>
-      <c r="K35" s="98"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="99"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="111"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="111"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="111"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="111"/>
+      <c r="M35" s="112"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>

--- a/RAMON FRANCO/Octubre/CALCULO EDESUR RAMON FRANCO Octubre.xlsx
+++ b/RAMON FRANCO/Octubre/CALCULO EDESUR RAMON FRANCO Octubre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B25AC0-F941-41D5-8373-376777E91A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13355AD3-C467-453D-8976-F0B3A8D2AB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -339,7 +339,7 @@
     <t>QUIENES ADEUDEN DOS MESES DE EDESUR SERAN DESCONECTADOS DE LA RED. SALUDOS CORDIALES.</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 15/10</t>
+    <t>EDESUR - VENCIMIENTO 14/11</t>
   </si>
 </sst>
 </file>
